--- a/Team-Data/2007-08/2-2-2007-08.xlsx
+++ b/Team-Data/2007-08/2-2-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,88 +728,88 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
         <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>0.455</v>
+        <v>0.442</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="J2" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.442</v>
+        <v>0.44</v>
       </c>
       <c r="L2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="M2" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.318</v>
+        <v>0.32</v>
       </c>
       <c r="O2" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="P2" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.773</v>
+        <v>0.771</v>
       </c>
       <c r="R2" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S2" t="n">
-        <v>29.7</v>
+        <v>29.9</v>
       </c>
       <c r="T2" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U2" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V2" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W2" t="n">
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>94.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.3</v>
+        <v>-1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF2" t="n">
         <v>17</v>
@@ -754,7 +821,7 @@
         <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ2" t="n">
         <v>22</v>
@@ -766,7 +833,7 @@
         <v>29</v>
       </c>
       <c r="AM2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AN2" t="n">
         <v>29</v>
@@ -781,31 +848,31 @@
         <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AV2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
         <v>3</v>
       </c>
       <c r="AY2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -933,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
         <v>25</v>
@@ -957,7 +1024,7 @@
         <v>8</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
@@ -981,13 +1048,13 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
         <v>7</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -1025,25 +1092,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" t="n">
         <v>18</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.375</v>
+        <v>0.383</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J4" t="n">
-        <v>79.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="K4" t="n">
         <v>0.449</v>
@@ -1052,31 +1119,31 @@
         <v>6.2</v>
       </c>
       <c r="M4" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="O4" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P4" t="n">
         <v>25.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.701</v>
+        <v>0.704</v>
       </c>
       <c r="R4" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="S4" t="n">
         <v>29.4</v>
       </c>
       <c r="T4" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
       <c r="U4" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V4" t="n">
         <v>15.2</v>
@@ -1085,7 +1152,7 @@
         <v>7.5</v>
       </c>
       <c r="X4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
         <v>5.8</v>
@@ -1097,22 +1164,22 @@
         <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.5</v>
+        <v>-4.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
         <v>5</v>
@@ -1121,10 +1188,10 @@
         <v>23</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>16</v>
@@ -1133,37 +1200,37 @@
         <v>16</v>
       </c>
       <c r="AN4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
         <v>30</v>
       </c>
       <c r="AR4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="n">
         <v>25</v>
       </c>
       <c r="AT4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU4" t="n">
         <v>10</v>
       </c>
       <c r="AV4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
         <v>28</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" t="n">
         <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>0.391</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1225,31 +1292,31 @@
         <v>35.5</v>
       </c>
       <c r="J5" t="n">
-        <v>84.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.42</v>
+        <v>0.419</v>
       </c>
       <c r="L5" t="n">
         <v>5.4</v>
       </c>
       <c r="M5" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.339</v>
+        <v>0.337</v>
       </c>
       <c r="O5" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="P5" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.751</v>
+        <v>0.749</v>
       </c>
       <c r="R5" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="S5" t="n">
         <v>30</v>
@@ -1258,10 +1325,10 @@
         <v>43.8</v>
       </c>
       <c r="U5" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V5" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W5" t="n">
         <v>7.6</v>
@@ -1273,19 +1340,19 @@
         <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>94</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.1</v>
+        <v>-3</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1318,13 +1385,13 @@
         <v>19</v>
       </c>
       <c r="AO5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP5" t="n">
         <v>21</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1339,25 +1406,25 @@
         <v>20</v>
       </c>
       <c r="AV5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
         <v>13</v>
       </c>
       <c r="AX5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY5" t="n">
         <v>27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
         <v>16</v>
       </c>
       <c r="BB5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="H6" t="n">
         <v>48.8</v>
@@ -1407,37 +1474,37 @@
         <v>36</v>
       </c>
       <c r="J6" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L6" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M6" t="n">
         <v>18.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.353</v>
+        <v>0.355</v>
       </c>
       <c r="O6" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P6" t="n">
-        <v>25.5</v>
+        <v>25.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.722</v>
+        <v>0.724</v>
       </c>
       <c r="R6" t="n">
         <v>13.2</v>
       </c>
       <c r="S6" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T6" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="U6" t="n">
         <v>19.3</v>
@@ -1446,10 +1513,10 @@
         <v>14.5</v>
       </c>
       <c r="W6" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y6" t="n">
         <v>4.8</v>
@@ -1458,16 +1525,16 @@
         <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.6</v>
+        <v>-0.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
         <v>14</v>
@@ -1503,7 +1570,7 @@
         <v>15</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
         <v>25</v>
@@ -1512,10 +1579,10 @@
         <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU6" t="n">
         <v>26</v>
@@ -1527,16 +1594,16 @@
         <v>9</v>
       </c>
       <c r="AX6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ6" t="n">
         <v>22</v>
       </c>
       <c r="BA6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB6" t="n">
         <v>16</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
         <v>5</v>
@@ -1694,7 +1761,7 @@
         <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>15</v>
@@ -1718,10 +1785,10 @@
         <v>23</v>
       </c>
       <c r="BA7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
         <v>7</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F8" t="n">
         <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>0.609</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
@@ -1771,10 +1838,10 @@
         <v>38.4</v>
       </c>
       <c r="J8" t="n">
-        <v>84.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="K8" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L8" t="n">
         <v>6.1</v>
@@ -1783,19 +1850,19 @@
         <v>18.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.333</v>
+        <v>0.331</v>
       </c>
       <c r="O8" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="P8" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0.757</v>
       </c>
       <c r="R8" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S8" t="n">
         <v>33</v>
@@ -1807,31 +1874,31 @@
         <v>23.4</v>
       </c>
       <c r="V8" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W8" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA8" t="n">
         <v>24.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>106.3</v>
+        <v>106.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1840,7 +1907,7 @@
         <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
         <v>20</v>
@@ -1861,7 +1928,7 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1876,16 +1943,16 @@
         <v>10</v>
       </c>
       <c r="AS8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
         <v>2</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1897,7 +1964,7 @@
         <v>20</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2031,10 +2098,10 @@
         <v>14</v>
       </c>
       <c r="AJ9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL9" t="n">
         <v>19</v>
@@ -2043,7 +2110,7 @@
         <v>23</v>
       </c>
       <c r="AN9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO9" t="n">
         <v>13</v>
@@ -2061,7 +2128,7 @@
         <v>26</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU9" t="n">
         <v>9</v>
@@ -2082,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="BA9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB9" t="n">
         <v>15</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -2195,19 +2262,19 @@
         <v>2.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF10" t="n">
         <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2225,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO10" t="n">
         <v>12</v>
@@ -2234,7 +2301,7 @@
         <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR10" t="n">
         <v>9</v>
@@ -2243,7 +2310,7 @@
         <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
@@ -2258,7 +2325,7 @@
         <v>20</v>
       </c>
       <c r="AY10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ10" t="n">
         <v>27</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -2299,64 +2366,64 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11" t="n">
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>0.574</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J11" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L11" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M11" t="n">
         <v>19.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.335</v>
+        <v>0.336</v>
       </c>
       <c r="O11" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="P11" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.727</v>
+        <v>0.729</v>
       </c>
       <c r="R11" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S11" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="T11" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="U11" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V11" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W11" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X11" t="n">
         <v>5.5</v>
@@ -2365,22 +2432,22 @@
         <v>4.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="AA11" t="n">
         <v>20.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>95.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF11" t="n">
         <v>13</v>
@@ -2395,19 +2462,19 @@
         <v>16</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM11" t="n">
         <v>8</v>
       </c>
       <c r="AN11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO11" t="n">
         <v>26</v>
@@ -2422,7 +2489,7 @@
         <v>7</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
@@ -2434,16 +2501,16 @@
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX11" t="n">
         <v>4</v>
       </c>
       <c r="AY11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>8</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>6</v>
       </c>
       <c r="BA11" t="n">
         <v>20</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12" t="n">
         <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G12" t="n">
-        <v>0.396</v>
+        <v>0.404</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2505,46 +2572,46 @@
         <v>0.443</v>
       </c>
       <c r="L12" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0.368</v>
+        <v>0.366</v>
       </c>
       <c r="O12" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P12" t="n">
         <v>24</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="R12" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S12" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T12" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="U12" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V12" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="W12" t="n">
         <v>7.7</v>
       </c>
       <c r="X12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z12" t="n">
         <v>24.4</v>
@@ -2553,16 +2620,16 @@
         <v>21.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.4</v>
+        <v>103.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2</v>
+        <v>-1.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="n">
         <v>21</v>
@@ -2592,7 +2659,7 @@
         <v>10</v>
       </c>
       <c r="AO12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP12" t="n">
         <v>20</v>
@@ -2601,16 +2668,16 @@
         <v>12</v>
       </c>
       <c r="AR12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
@@ -2619,7 +2686,7 @@
         <v>10</v>
       </c>
       <c r="AX12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
         <v>21</v>
@@ -2634,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E13" t="n">
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G13" t="n">
-        <v>0.318</v>
+        <v>0.326</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
@@ -2681,43 +2748,43 @@
         <v>34.7</v>
       </c>
       <c r="J13" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="M13" t="n">
         <v>12.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.326</v>
+        <v>0.328</v>
       </c>
       <c r="O13" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="P13" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="Q13" t="n">
         <v>0.782</v>
       </c>
       <c r="R13" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S13" t="n">
         <v>31.3</v>
       </c>
       <c r="T13" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U13" t="n">
         <v>21.5</v>
       </c>
       <c r="V13" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W13" t="n">
         <v>6.7</v>
@@ -2732,22 +2799,22 @@
         <v>21.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>-5</v>
+        <v>-4.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
       </c>
       <c r="AF13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
         <v>25</v>
@@ -2756,7 +2823,7 @@
         <v>18</v>
       </c>
       <c r="AI13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ13" t="n">
         <v>21</v>
@@ -2765,7 +2832,7 @@
         <v>26</v>
       </c>
       <c r="AL13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM13" t="n">
         <v>27</v>
@@ -2786,31 +2853,31 @@
         <v>28</v>
       </c>
       <c r="AS13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AU13" t="n">
         <v>13</v>
       </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
         <v>22</v>
       </c>
       <c r="AX13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ13" t="n">
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>5.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2953,19 +3020,19 @@
         <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP14" t="n">
         <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2992,13 +3059,13 @@
         <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E15" t="n">
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>0.277</v>
+        <v>0.283</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
@@ -3054,34 +3121,34 @@
         <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="O15" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P15" t="n">
         <v>24.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.743</v>
+        <v>0.745</v>
       </c>
       <c r="R15" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S15" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T15" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U15" t="n">
         <v>20.3</v>
       </c>
       <c r="V15" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="W15" t="n">
         <v>5.8</v>
@@ -3096,16 +3163,16 @@
         <v>19.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.9</v>
+        <v>101.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>-4.7</v>
+        <v>-4.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,13 +3184,13 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI15" t="n">
         <v>10</v>
       </c>
       <c r="AJ15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK15" t="n">
         <v>7</v>
@@ -3135,13 +3202,13 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ15" t="n">
         <v>20</v>
@@ -3168,16 +3235,16 @@
         <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
       </c>
       <c r="BB15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC15" t="n">
         <v>23</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-7.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3302,7 +3369,7 @@
         <v>12</v>
       </c>
       <c r="AI16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ16" t="n">
         <v>29</v>
@@ -3317,7 +3384,7 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>18</v>
@@ -3347,7 +3414,7 @@
         <v>19</v>
       </c>
       <c r="AX16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY16" t="n">
         <v>3</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -3391,94 +3458,94 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E17" t="n">
         <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.375</v>
+        <v>0.383</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J17" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.447</v>
+        <v>0.449</v>
       </c>
       <c r="L17" t="n">
         <v>5.6</v>
       </c>
       <c r="M17" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="O17" t="n">
         <v>16.6</v>
       </c>
-      <c r="N17" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="O17" t="n">
-        <v>16.5</v>
-      </c>
       <c r="P17" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q17" t="n">
         <v>0.741</v>
       </c>
       <c r="R17" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S17" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U17" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V17" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="W17" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z17" t="n">
         <v>21.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>94</v>
+        <v>94.2</v>
       </c>
       <c r="AC17" t="n">
         <v>-6.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH17" t="n">
         <v>10</v>
@@ -3487,49 +3554,49 @@
         <v>20</v>
       </c>
       <c r="AJ17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK17" t="n">
         <v>19</v>
       </c>
       <c r="AL17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM17" t="n">
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
         <v>27</v>
       </c>
       <c r="AP17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AQ17" t="n">
         <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS17" t="n">
         <v>30</v>
       </c>
       <c r="AT17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AV17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW17" t="n">
         <v>21</v>
       </c>
       <c r="AX17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY17" t="n">
         <v>23</v>
@@ -3538,10 +3605,10 @@
         <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BC17" t="n">
         <v>27</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-7.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3666,7 +3733,7 @@
         <v>29</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>8</v>
@@ -3681,7 +3748,7 @@
         <v>22</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3696,16 +3763,16 @@
         <v>5</v>
       </c>
       <c r="AS18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW18" t="n">
         <v>18</v>
@@ -3714,7 +3781,7 @@
         <v>29</v>
       </c>
       <c r="AY18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ18" t="n">
         <v>28</v>
@@ -3723,7 +3790,7 @@
         <v>29</v>
       </c>
       <c r="BB18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E19" t="n">
         <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.426</v>
+        <v>0.435</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
@@ -3773,10 +3840,10 @@
         <v>33.7</v>
       </c>
       <c r="J19" t="n">
-        <v>77.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="K19" t="n">
-        <v>0.435</v>
+        <v>0.433</v>
       </c>
       <c r="L19" t="n">
         <v>5.6</v>
@@ -3785,37 +3852,37 @@
         <v>16.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.331</v>
+        <v>0.332</v>
       </c>
       <c r="O19" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="P19" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.716</v>
+        <v>0.714</v>
       </c>
       <c r="R19" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S19" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T19" t="n">
-        <v>42.1</v>
+        <v>42.4</v>
       </c>
       <c r="U19" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V19" t="n">
         <v>15.7</v>
       </c>
       <c r="W19" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y19" t="n">
         <v>4.5</v>
@@ -3824,16 +3891,16 @@
         <v>22.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.7</v>
+        <v>-5.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
@@ -3845,7 +3912,7 @@
         <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3857,7 +3924,7 @@
         <v>29</v>
       </c>
       <c r="AL19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM19" t="n">
         <v>18</v>
@@ -3875,19 +3942,19 @@
         <v>27</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AU19" t="n">
         <v>3</v>
       </c>
       <c r="AV19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
         <v>25</v>
@@ -3902,7 +3969,7 @@
         <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BB19" t="n">
         <v>29</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>6.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -4057,7 +4124,7 @@
         <v>7</v>
       </c>
       <c r="AR20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS20" t="n">
         <v>12</v>
@@ -4072,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E21" t="n">
         <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G21" t="n">
-        <v>0.298</v>
+        <v>0.304</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="J21" t="n">
-        <v>80.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="K21" t="n">
         <v>0.438</v>
@@ -4149,7 +4216,7 @@
         <v>16.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="O21" t="n">
         <v>18.7</v>
@@ -4158,16 +4225,16 @@
         <v>26</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.717</v>
+        <v>0.719</v>
       </c>
       <c r="R21" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="S21" t="n">
         <v>29.4</v>
       </c>
       <c r="T21" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="U21" t="n">
         <v>18.2</v>
@@ -4176,28 +4243,28 @@
         <v>15.3</v>
       </c>
       <c r="W21" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="X21" t="n">
         <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z21" t="n">
         <v>21.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>94.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6</v>
+        <v>-6.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
@@ -4209,16 +4276,16 @@
         <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK21" t="n">
         <v>27</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>25</v>
       </c>
       <c r="AL21" t="n">
         <v>22</v>
@@ -4239,7 +4306,7 @@
         <v>26</v>
       </c>
       <c r="AR21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AS21" t="n">
         <v>24</v>
@@ -4251,16 +4318,16 @@
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ21" t="n">
         <v>17</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E22" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F22" t="n">
         <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>0.633</v>
+        <v>0.625</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,31 +4386,31 @@
         <v>36.6</v>
       </c>
       <c r="J22" t="n">
-        <v>78.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.469</v>
+        <v>0.467</v>
       </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="M22" t="n">
         <v>24.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.366</v>
+        <v>0.362</v>
       </c>
       <c r="O22" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="P22" t="n">
-        <v>29.6</v>
+        <v>29.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="R22" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S22" t="n">
         <v>32.9</v>
@@ -4352,13 +4419,13 @@
         <v>42.6</v>
       </c>
       <c r="U22" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V22" t="n">
         <v>15</v>
       </c>
       <c r="W22" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X22" t="n">
         <v>4.5</v>
@@ -4367,22 +4434,22 @@
         <v>4.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>103.8</v>
+        <v>103.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF22" t="n">
         <v>8</v>
@@ -4394,7 +4461,7 @@
         <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ22" t="n">
         <v>26</v>
@@ -4403,16 +4470,16 @@
         <v>6</v>
       </c>
       <c r="AL22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM22" t="n">
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AP22" t="n">
         <v>2</v>
@@ -4424,7 +4491,7 @@
         <v>27</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT22" t="n">
         <v>9</v>
@@ -4436,16 +4503,16 @@
         <v>15</v>
       </c>
       <c r="AW22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY22" t="n">
         <v>6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -4561,34 +4628,34 @@
         <v>-2</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>21</v>
       </c>
       <c r="AF23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG23" t="n">
         <v>22</v>
       </c>
       <c r="AH23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ23" t="n">
         <v>16</v>
       </c>
       <c r="AK23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
       </c>
       <c r="AM23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AN23" t="n">
         <v>30</v>
@@ -4615,7 +4682,7 @@
         <v>24</v>
       </c>
       <c r="AV23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW23" t="n">
         <v>6</v>
@@ -4633,7 +4700,7 @@
         <v>19</v>
       </c>
       <c r="BB23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC23" t="n">
         <v>19</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>6</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4767,7 +4834,7 @@
         <v>1</v>
       </c>
       <c r="AL24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM24" t="n">
         <v>4</v>
@@ -4776,10 +4843,10 @@
         <v>3</v>
       </c>
       <c r="AO24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ24" t="n">
         <v>5</v>
@@ -4809,10 +4876,10 @@
         <v>2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>0.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF25" t="n">
         <v>11</v>
@@ -4937,7 +5004,7 @@
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI25" t="n">
         <v>22</v>
@@ -4958,7 +5025,7 @@
         <v>2</v>
       </c>
       <c r="AO25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP25" t="n">
         <v>22</v>
@@ -4970,7 +5037,7 @@
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT25" t="n">
         <v>28</v>
@@ -4985,13 +5052,13 @@
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY25" t="n">
         <v>4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F26" t="n">
         <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.478</v>
+        <v>0.467</v>
       </c>
       <c r="H26" t="n">
         <v>48.2</v>
       </c>
       <c r="I26" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J26" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.459</v>
+        <v>0.461</v>
       </c>
       <c r="L26" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M26" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N26" t="n">
-        <v>0.372</v>
+        <v>0.374</v>
       </c>
       <c r="O26" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="P26" t="n">
-        <v>27.6</v>
+        <v>27.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.794</v>
+        <v>0.792</v>
       </c>
       <c r="R26" t="n">
         <v>10</v>
@@ -5092,22 +5159,22 @@
         <v>4.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>100.4</v>
+        <v>100.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.9</v>
+        <v>-2</v>
       </c>
       <c r="AD26" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>17</v>
@@ -5122,13 +5189,13 @@
         <v>20</v>
       </c>
       <c r="AI26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>15</v>
@@ -5140,16 +5207,16 @@
         <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ26" t="n">
         <v>4</v>
       </c>
       <c r="AR26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS26" t="n">
         <v>23</v>
@@ -5158,13 +5225,13 @@
         <v>29</v>
       </c>
       <c r="AU26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV26" t="n">
         <v>29</v>
       </c>
       <c r="AW26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX26" t="n">
         <v>25</v>
@@ -5176,13 +5243,13 @@
         <v>24</v>
       </c>
       <c r="BA26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB26" t="n">
         <v>10</v>
       </c>
       <c r="BC26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -5289,10 +5356,10 @@
         <v>4.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF27" t="n">
         <v>6</v>
@@ -5307,7 +5374,7 @@
         <v>21</v>
       </c>
       <c r="AJ27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK27" t="n">
         <v>13</v>
@@ -5325,7 +5392,7 @@
         <v>25</v>
       </c>
       <c r="AP27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ27" t="n">
         <v>15</v>
@@ -5334,7 +5401,7 @@
         <v>25</v>
       </c>
       <c r="AS27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT27" t="n">
         <v>20</v>
@@ -5358,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="BA27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB27" t="n">
         <v>19</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -5393,37 +5460,37 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
         <v>35</v>
       </c>
       <c r="G28" t="n">
-        <v>0.255</v>
+        <v>0.239</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J28" t="n">
         <v>85.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L28" t="n">
         <v>4.2</v>
       </c>
       <c r="M28" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.331</v>
+        <v>0.332</v>
       </c>
       <c r="O28" t="n">
         <v>17.5</v>
@@ -5435,19 +5502,19 @@
         <v>0.767</v>
       </c>
       <c r="R28" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S28" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="T28" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
       <c r="U28" t="n">
         <v>21.4</v>
       </c>
       <c r="V28" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="W28" t="n">
         <v>6.6</v>
@@ -5456,22 +5523,22 @@
         <v>5.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA28" t="n">
         <v>20</v>
       </c>
       <c r="AB28" t="n">
-        <v>96.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>-7.5</v>
+        <v>-7.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="n">
         <v>28</v>
@@ -5483,7 +5550,7 @@
         <v>28</v>
       </c>
       <c r="AH28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
@@ -5492,7 +5559,7 @@
         <v>3</v>
       </c>
       <c r="AK28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL28" t="n">
         <v>26</v>
@@ -5501,7 +5568,7 @@
         <v>26</v>
       </c>
       <c r="AN28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO28" t="n">
         <v>24</v>
@@ -5513,7 +5580,7 @@
         <v>11</v>
       </c>
       <c r="AR28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS28" t="n">
         <v>2</v>
@@ -5531,16 +5598,16 @@
         <v>24</v>
       </c>
       <c r="AX28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY28" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ28" t="n">
         <v>12</v>
       </c>
       <c r="BA28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB28" t="n">
         <v>17</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>2.9</v>
       </c>
       <c r="AD29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE29" t="n">
         <v>14</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>15</v>
       </c>
       <c r="AF29" t="n">
         <v>15</v>
@@ -5665,13 +5732,13 @@
         <v>15</v>
       </c>
       <c r="AH29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI29" t="n">
         <v>9</v>
       </c>
       <c r="AJ29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK29" t="n">
         <v>10</v>
@@ -5695,13 +5762,13 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS29" t="n">
         <v>15</v>
       </c>
       <c r="AT29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU29" t="n">
         <v>8</v>
@@ -5716,10 +5783,10 @@
         <v>26</v>
       </c>
       <c r="AY29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -5757,64 +5824,64 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F30" t="n">
         <v>18</v>
       </c>
       <c r="G30" t="n">
-        <v>0.625</v>
+        <v>0.617</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>39.8</v>
+        <v>39.6</v>
       </c>
       <c r="J30" t="n">
-        <v>80.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0.492</v>
       </c>
       <c r="L30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M30" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="N30" t="n">
         <v>0.357</v>
       </c>
       <c r="O30" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="P30" t="n">
-        <v>28.4</v>
+        <v>28.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R30" t="n">
         <v>11.6</v>
       </c>
       <c r="S30" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="T30" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
       <c r="U30" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="V30" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X30" t="n">
         <v>4.4</v>
@@ -5823,19 +5890,19 @@
         <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="AA30" t="n">
         <v>23.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>105.1</v>
+        <v>105</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>7</v>
@@ -5853,22 +5920,22 @@
         <v>3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK30" t="n">
         <v>2</v>
       </c>
       <c r="AL30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AN30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP30" t="n">
         <v>5</v>
@@ -5883,22 +5950,22 @@
         <v>28</v>
       </c>
       <c r="AT30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ30" t="n">
         <v>30</v>
@@ -5910,7 +5977,7 @@
         <v>5</v>
       </c>
       <c r="BC30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6035,13 +6102,13 @@
         <v>15</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM31" t="n">
         <v>10</v>
@@ -6053,7 +6120,7 @@
         <v>11</v>
       </c>
       <c r="AP31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ31" t="n">
         <v>3</v>
@@ -6062,7 +6129,7 @@
         <v>8</v>
       </c>
       <c r="AS31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
@@ -6074,7 +6141,7 @@
         <v>9</v>
       </c>
       <c r="AW31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-2-2007-08</t>
+          <t>2008-02-02</t>
         </is>
       </c>
     </row>
